--- a/Config/Excel/GameConfig/UnitCombatConfig.xlsx
+++ b/Config/Excel/GameConfig/UnitCombatConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,20 +444,25 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>AutoBattleStrategyId</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>MoveSpeed</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>AutoCastNormalAttack</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>DefaultTargetPolicy</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Desc</t>
         </is>
@@ -491,20 +496,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>int#ref=AutoBattleStrategyConfigCategory</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>float</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -538,20 +548,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>自动战斗策略配置ID</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>移动速度（米/秒）</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>是否自动释放普攻</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>默认目标策略</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>描述</t>
         </is>
@@ -573,19 +588,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G4" t="b">
+        <v>5001</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H4" t="b">
         <v>1</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>NearestEnemy</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>玩家默认普攻绑定</t>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>玩家割草体验版：更快移动、更快收怪</t>
         </is>
       </c>
     </row>
@@ -605,19 +623,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G5" t="b">
+        <v>5001</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H5" t="b">
         <v>1</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>NearestEnemy</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>玩家默认普攻绑定</t>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>玩家割草体验版：更快移动、更快收怪</t>
         </is>
       </c>
     </row>
@@ -637,19 +658,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G6" t="b">
+        <v>5001</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H6" t="b">
         <v>1</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>NearestEnemy</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>玩家默认普攻绑定</t>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>玩家割草体验版：更快移动、更快收怪</t>
         </is>
       </c>
     </row>
@@ -669,19 +693,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G7" t="b">
+        <v>5001</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H7" t="b">
         <v>1</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>NearestEnemy</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>玩家默认普攻绑定</t>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>玩家割草体验版：更快移动、更快收怪</t>
         </is>
       </c>
     </row>
@@ -701,17 +728,20 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G8" t="b">
+        <v>5002</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H8" t="b">
         <v>1</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>NearestEnemy</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>普通怪物普攻绑定</t>
         </is>
@@ -733,17 +763,20 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G9" t="b">
+        <v>5002</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H9" t="b">
         <v>1</v>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>NearestEnemy</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>普通怪物普攻绑定</t>
         </is>
@@ -765,17 +798,20 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="G10" t="b">
+        <v>5003</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H10" t="b">
         <v>1</v>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>NearestEnemy</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>精英怪物普攻绑定</t>
         </is>
@@ -797,17 +833,20 @@
         </is>
       </c>
       <c r="F11" t="n">
+        <v>5003</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H11" t="b">
         <v>1</v>
       </c>
-      <c r="G11" t="b">
-        <v>1</v>
-      </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>NearestEnemy</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>精英怪物普攻绑定</t>
         </is>
@@ -829,17 +868,20 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G12" t="b">
+        <v>5004</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H12" t="b">
         <v>1</v>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>NearestEnemy</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>Boss普攻绑定</t>
         </is>

--- a/Config/Excel/GameConfig/UnitCombatConfig.xlsx
+++ b/Config/Excel/GameConfig/UnitCombatConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,25 +444,20 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>AutoBattleStrategyId</t>
+          <t>MoveSpeed</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>MoveSpeed</t>
+          <t>AutoCastNormalAttack</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>AutoCastNormalAttack</t>
+          <t>DefaultTargetPolicy</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>DefaultTargetPolicy</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>Desc</t>
         </is>
@@ -496,25 +491,20 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>int#ref=AutoBattleStrategyConfigCategory</t>
+          <t>float</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>string</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -548,25 +538,20 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>自动战斗策略配置ID</t>
+          <t>移动速度（米/秒）</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>移动速度（米/秒）</t>
+          <t>是否自动释放普攻</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>是否自动释放普攻</t>
+          <t>默认目标策略</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>默认目标策略</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
         <is>
           <t>描述</t>
         </is>
@@ -574,314 +559,159 @@
     </row>
     <row r="4">
       <c r="B4" t="n">
-        <v>1001</v>
+        <v>3001</v>
       </c>
       <c r="C4" t="n">
-        <v>1001</v>
+        <v>3001</v>
       </c>
       <c r="D4" t="n">
-        <v>11001</v>
+        <v>21001</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>11001</t>
+          <t>21001</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5001</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="H4" t="b">
+        <v>0.6</v>
+      </c>
+      <c r="G4" t="b">
         <v>1</v>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>NearestEnemy</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>NearestEnemy</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>玩家割草体验版：更快移动、更快收怪</t>
+          <t>普通怪物普攻绑定</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="n">
-        <v>1002</v>
+        <v>3002</v>
       </c>
       <c r="C5" t="n">
-        <v>1002</v>
+        <v>3002</v>
       </c>
       <c r="D5" t="n">
-        <v>11001</v>
+        <v>21001</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11001</t>
+          <t>21001</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>5001</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="H5" t="b">
+        <v>0.75</v>
+      </c>
+      <c r="G5" t="b">
         <v>1</v>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NearestEnemy</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>NearestEnemy</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>玩家割草体验版：更快移动、更快收怪</t>
+          <t>普通怪物普攻绑定</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="n">
-        <v>1003</v>
+        <v>3003</v>
       </c>
       <c r="C6" t="n">
-        <v>1003</v>
+        <v>3003</v>
       </c>
       <c r="D6" t="n">
-        <v>11001</v>
+        <v>21002</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11001</t>
+          <t>21002</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5001</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="H6" t="b">
+        <v>0.6</v>
+      </c>
+      <c r="G6" t="b">
         <v>1</v>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>NearestEnemy</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>NearestEnemy</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>玩家割草体验版：更快移动、更快收怪</t>
+          <t>精英怪物普攻绑定</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="n">
-        <v>1004</v>
+        <v>3004</v>
       </c>
       <c r="C7" t="n">
-        <v>1004</v>
+        <v>3004</v>
       </c>
       <c r="D7" t="n">
-        <v>11001</v>
+        <v>21002</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11001</t>
+          <t>21002</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5001</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="H7" t="b">
+        <v>0.85</v>
+      </c>
+      <c r="G7" t="b">
         <v>1</v>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NearestEnemy</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>NearestEnemy</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>玩家割草体验版：更快移动、更快收怪</t>
+          <t>精英怪物普攻绑定</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="n">
-        <v>3001</v>
+        <v>3005</v>
       </c>
       <c r="C8" t="n">
-        <v>3001</v>
+        <v>3005</v>
       </c>
       <c r="D8" t="n">
-        <v>21001</v>
+        <v>21003</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>21001</t>
+          <t>21003</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5002</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H8" t="b">
+        <v>0.45</v>
+      </c>
+      <c r="G8" t="b">
         <v>1</v>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>NearestEnemy</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
-        <is>
-          <t>NearestEnemy</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>普通怪物普攻绑定</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" t="n">
-        <v>3002</v>
-      </c>
-      <c r="C9" t="n">
-        <v>3002</v>
-      </c>
-      <c r="D9" t="n">
-        <v>21001</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>21001</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>5002</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H9" t="b">
-        <v>1</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>NearestEnemy</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>普通怪物普攻绑定</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" t="n">
-        <v>3003</v>
-      </c>
-      <c r="C10" t="n">
-        <v>3003</v>
-      </c>
-      <c r="D10" t="n">
-        <v>21002</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>21002</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>5003</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>NearestEnemy</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>精英怪物普攻绑定</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" t="n">
-        <v>3004</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3004</v>
-      </c>
-      <c r="D11" t="n">
-        <v>21002</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>21002</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>5003</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="H11" t="b">
-        <v>1</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>NearestEnemy</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>精英怪物普攻绑定</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" t="n">
-        <v>3005</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3005</v>
-      </c>
-      <c r="D12" t="n">
-        <v>21003</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>21003</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>5004</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H12" t="b">
-        <v>1</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>NearestEnemy</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
         <is>
           <t>Boss普攻绑定</t>
         </is>

--- a/Config/Excel/GameConfig/UnitCombatConfig.xlsx
+++ b/Config/Excel/GameConfig/UnitCombatConfig.xlsx
@@ -2,39 +2,375 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="15320" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="UnitCombatConfig" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="21">
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -42,15 +378,305 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -403,7 +1029,6 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -413,8 +1038,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="7"/>
+  <cols>
+    <col width="26.4423076923077" customWidth="1" min="4" max="4"/>
+    <col width="27.0769230769231" customWidth="1" min="5" max="5"/>
+    <col width="36.5384615384615" customWidth="1" min="6" max="6"/>
+    <col width="33.3269230769231" customWidth="1" min="7" max="7"/>
+    <col width="28.0480769230769" customWidth="1" min="8" max="8"/>
+    <col width="36.6923076923077" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -434,12 +1067,12 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>NormalAttackSkillId</t>
+          <t>NormalAttackEmitterId</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>AutoSkillIds</t>
+          <t>AutoEmitterIds</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -481,12 +1114,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>int#ref=SkillConfigCategory</t>
+          <t>int#ref=EmitterConfigCategory</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>array,int#sep=,</t>
+          <t>(array#sep=,),int#ref=EmitterConfigCategory</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -528,12 +1161,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>默认普攻技能ID</t>
+          <t>默认普攻发射器ID</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI自动择优技能列表（为空则回退普攻）</t>
+          <t>AI自动择优发射器列表（为空则回退普攻）</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -633,7 +1266,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>21002</t>
+          <t>21005</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -649,7 +1282,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>精英怪物普攻绑定</t>
+          <t>精英怪物-眩晕攻击</t>
         </is>
       </c>
     </row>
@@ -665,7 +1298,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>21002</t>
+          <t>21004</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -681,7 +1314,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>精英怪物普攻绑定</t>
+          <t>精英怪物-毒DOT减速攻击</t>
         </is>
       </c>
     </row>
@@ -697,7 +1330,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>21003</t>
+          <t>21006</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -713,7 +1346,71 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Boss普攻绑定</t>
+          <t>Boss炎魔-毒息DOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>3006</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3006</v>
+      </c>
+      <c r="D9" t="n">
+        <v>21003</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>21007</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>NearestEnemy</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Boss冰龙-冰冻攻击</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>3007</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>11001</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>11001</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>NearestEnemy</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>玩家英雄-普攻（多技能待Luban修复后配置）</t>
         </is>
       </c>
     </row>
